--- a/pricing/商务成品/对外/定制报价/Trinity模型报价表_主力模型定制.xlsx
+++ b/pricing/商务成品/对外/定制报价/Trinity模型报价表_主力模型定制.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +45,22 @@
     <font>
       <name val="Menlo"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00713F12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001D2939"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -102,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -157,12 +174,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyFill="1" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -597,6 +640,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>本页为累积更新日志（新→旧），供 Trinity 对内核对；外发客户前可删本页。文件：Trinity模型报价表_主力模型定制.xlsx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>更新说明</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026.9.20</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>主力定制</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>启用「更新」累积日志；本轮 7 款</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>定制表 · 首启</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -612,363 +729,363 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Trinity · 折扣报价表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>模态</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>厂商</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>模型 ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输入</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输出</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>刊例价·缓存</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>折扣</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>线路</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>生文</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>月之暗面</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>kimi-k3</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Kimi K3</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>15.39</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>6.3折</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Wawa</t>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>9.2折</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>数据宝</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>智谱</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>glm-5.2</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>GLM-5.2</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>4.40</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>6折</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Wawa</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>deepseek-v4-pro</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>DeepSeek V4 Pro Direct</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>原价</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>deepseek官方</t>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>7.2折</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>数据宝</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>阿里云·通义</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>qwen3.8-max</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Qwen3.8 Max</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>7.2折</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>阿里云百炼-国内</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>gpt-5.6-sol</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>7.7折</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Azure</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>claude-opus-5</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>9.2折</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>生视频</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>字节·即梦</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>seedance-2.0-overseas-hc-os</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>Seedance 2.0 Overseas HC</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>7.00（720p）</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>9.9折</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Opensand-国际</t>
         </is>
